--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/SRFormer2/SRFormer2+50T+50EP+optim_purn/params_vs_psnr_analysis/SRFormer_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/SRFormer2/SRFormer2+50T+50EP+optim_purn/params_vs_psnr_analysis/SRFormer_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>375728</v>
       </c>
       <c r="C2" t="n">
+        <v>0.532461312</v>
+      </c>
+      <c r="D2" t="n">
         <v>28.68567848205566</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>478420</v>
       </c>
       <c r="C3" t="n">
+        <v>0.70953912</v>
+      </c>
+      <c r="D3" t="n">
         <v>27.63242301940918</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>574166</v>
       </c>
       <c r="C4" t="n">
+        <v>0.853496012</v>
+      </c>
+      <c r="D4" t="n">
         <v>27.29326095581055</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>538136</v>
       </c>
       <c r="C5" t="n">
+        <v>0.861195456</v>
+      </c>
+      <c r="D5" t="n">
         <v>27.70898895263672</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>143644</v>
       </c>
       <c r="C6" t="n">
+        <v>0.234716208</v>
+      </c>
+      <c r="D6" t="n">
         <v>27.91423835754394</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>312672</v>
       </c>
       <c r="C7" t="n">
+        <v>0.464754432</v>
+      </c>
+      <c r="D7" t="n">
         <v>27.77197608947754</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>547928</v>
       </c>
       <c r="C8" t="n">
+        <v>0.88709344</v>
+      </c>
+      <c r="D8" t="n">
         <v>27.95370635986328</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>326686</v>
       </c>
       <c r="C9" t="n">
+        <v>0.444021868</v>
+      </c>
+      <c r="D9" t="n">
         <v>29.67362060546875</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>245168</v>
       </c>
       <c r="C10" t="n">
+        <v>0.394269952</v>
+      </c>
+      <c r="D10" t="n">
         <v>20.93247566223145</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>456640</v>
       </c>
       <c r="C11" t="n">
+        <v>0.6259269119999999</v>
+      </c>
+      <c r="D11" t="n">
         <v>28.98331031799317</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>1615504</v>
       </c>
       <c r="C12" t="n">
+        <v>2.031102976</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.16123313903809</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>1615504</v>
       </c>
       <c r="C13" t="n">
+        <v>2.031102976</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.14192695617676</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>1615504</v>
       </c>
       <c r="C14" t="n">
+        <v>2.031102976</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.14807777404785</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>1383392</v>
       </c>
       <c r="C15" t="n">
+        <v>1.834355712</v>
+      </c>
+      <c r="D15" t="n">
         <v>29.98004493713379</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>1066508</v>
       </c>
       <c r="C16" t="n">
+        <v>1.42148856</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.27306976318359</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>1066508</v>
       </c>
       <c r="C17" t="n">
+        <v>1.418695056</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.24274101257324</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>1066508</v>
       </c>
       <c r="C18" t="n">
+        <v>1.418695056</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.10407485961914</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>1145132</v>
       </c>
       <c r="C19" t="n">
+        <v>1.599070608</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.3240592956543</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>1144844</v>
       </c>
       <c r="C20" t="n">
+        <v>1.59904728</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.33113746643066</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>991226</v>
       </c>
       <c r="C21" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.30764122009277</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>991226</v>
       </c>
       <c r="C22" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.3703727722168</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>991226</v>
       </c>
       <c r="C23" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.28800964355469</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>1309518</v>
       </c>
       <c r="C24" t="n">
+        <v>1.824885612</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.36462135314941</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>1075438</v>
       </c>
       <c r="C25" t="n">
+        <v>1.583651628</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.37883644104004</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>1309518</v>
       </c>
       <c r="C26" t="n">
+        <v>1.824885612</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.45349769592285</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>1309518</v>
       </c>
       <c r="C27" t="n">
+        <v>1.824885612</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.32417602539062</v>
       </c>
     </row>
@@ -739,6 +822,9 @@
         <v>814970</v>
       </c>
       <c r="C28" t="n">
+        <v>1.2058587</v>
+      </c>
+      <c r="D28" t="n">
         <v>30.30941543579102</v>
       </c>
     </row>
@@ -750,6 +836,9 @@
         <v>843782</v>
       </c>
       <c r="C29" t="n">
+        <v>1.142319564</v>
+      </c>
+      <c r="D29" t="n">
         <v>30.2251350402832</v>
       </c>
     </row>
@@ -761,6 +850,9 @@
         <v>1144844</v>
       </c>
       <c r="C30" t="n">
+        <v>1.59904728</v>
+      </c>
+      <c r="D30" t="n">
         <v>30.36607513427735</v>
       </c>
     </row>
@@ -772,6 +864,9 @@
         <v>991226</v>
       </c>
       <c r="C31" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="D31" t="n">
         <v>30.35539321899414</v>
       </c>
     </row>
@@ -783,6 +878,9 @@
         <v>1543598</v>
       </c>
       <c r="C32" t="n">
+        <v>2.066119596</v>
+      </c>
+      <c r="D32" t="n">
         <v>30.4514907836914</v>
       </c>
     </row>
@@ -794,6 +892,9 @@
         <v>572498</v>
       </c>
       <c r="C33" t="n">
+        <v>0.780427756</v>
+      </c>
+      <c r="D33" t="n">
         <v>30.28403930664063</v>
       </c>
     </row>
